--- a/site/downloads/breeding-stock-depreciation.xlsx
+++ b/site/downloads/breeding-stock-depreciation.xlsx
@@ -590,7 +590,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Built by Lone Star Exotics Hub (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
+          <t>Built by Exotic Ranch &amp; Wildlife Network (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,6 @@
           <t>NOT tax, legal or investment advice. Educational template only. Consult a CPA and your county appraisal district.</t>
         </is>
       </c>
-      <c r="G1" s="7" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
